--- a/files/Layout.xlsx
+++ b/files/Layout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Mis documentos\GitHub\planPiso\app\static\angular\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mis documentos\GitHub\planPiso\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E97EB6-D808-41B6-84E8-BC4B208A6941}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F10FE98-60C3-4677-B34A-FF4A0E715A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="9675" windowWidth="29040" windowHeight="15840" xr2:uid="{1ADB4FD7-A697-46A7-86D6-8EA9EEB47067}"/>
+    <workbookView xWindow="3456" yWindow="3456" windowWidth="36864" windowHeight="18684" xr2:uid="{1ADB4FD7-A697-46A7-86D6-8EA9EEB47067}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Numeroserie</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>3N6AD33A3LK817990</t>
+  </si>
+  <si>
+    <t>Fecha</t>
   </si>
 </sst>
 </file>
@@ -89,9 +92,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -115,6 +120,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -130,12 +136,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8421711-38AC-4A70-BAEF-373FDDC4E814}" name="Tabla1" displayName="Tabla1" ref="A1:C4" totalsRowShown="0">
-  <autoFilter ref="A1:C4" xr:uid="{C664C210-EE0F-46A0-9C7E-E6090001C800}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8421711-38AC-4A70-BAEF-373FDDC4E814}" name="Tabla1" displayName="Tabla1" ref="A1:D4" totalsRowShown="0">
+  <autoFilter ref="A1:D4" xr:uid="{C664C210-EE0F-46A0-9C7E-E6090001C800}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{97CD01A3-7B84-4021-B2AB-A2BBAF1D572B}" name="Numeroserie"/>
     <tableColumn id="2" xr3:uid="{C99A62E6-FEF0-4734-A75D-397472FC07D5}" name="Valor" dataDxfId="0" dataCellStyle="Millares"/>
     <tableColumn id="3" xr3:uid="{3C8487B3-1545-4A58-9812-91DB5DD16850}" name="Interes"/>
+    <tableColumn id="4" xr3:uid="{E4415F32-236D-45EA-91D3-DB7ACB6204BD}" name="Fecha"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -438,59 +445,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B48DF34-8E4D-4AFF-846F-BD0853CBA404}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>223075</v>
       </c>
       <c r="C2">
         <v>1000</v>
       </c>
+      <c r="D2" s="3">
+        <v>44835</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>254723.24</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>294474.34999999998</v>
       </c>
       <c r="C4">
         <v>1000</v>
+      </c>
+      <c r="D4" s="3">
+        <v>44842</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
